--- a/SDPC_B10遥测数据表.xlsx
+++ b/SDPC_B10遥测数据表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="25005" windowHeight="12240"/>
   </bookViews>
   <sheets>
     <sheet name="遥测监控表" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="53">
   <si>
     <t>编号</t>
   </si>
@@ -87,50 +87,22 @@
     <t>b6</t>
   </si>
   <si>
-    <t>0x0:否
-0x2:是</t>
-  </si>
-  <si>
     <t>b5</t>
   </si>
   <si>
-    <t>0x0:否
-0x3:是</t>
-  </si>
-  <si>
     <t>b4</t>
   </si>
   <si>
-    <t>0x0:否
-0x4:是</t>
-  </si>
-  <si>
     <t>b3</t>
   </si>
   <si>
-    <t>0x0:否
-0x5:是</t>
-  </si>
-  <si>
     <t>b2</t>
   </si>
   <si>
-    <t>0x0:否
-0x6:是</t>
-  </si>
-  <si>
     <t>b1</t>
   </si>
   <si>
-    <t>0x0:否
-0x7:是</t>
-  </si>
-  <si>
     <t>b0</t>
-  </si>
-  <si>
-    <t>0x0:否
-0x8:是</t>
   </si>
   <si>
     <t>byte4-byte5</t>
@@ -1411,7 +1383,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>10</v>
@@ -1430,13 +1402,13 @@
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>10</v>
@@ -1455,13 +1427,13 @@
         <v>14</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>10</v>
@@ -1480,13 +1452,13 @@
         <v>14</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>10</v>
@@ -1505,13 +1477,13 @@
         <v>14</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>10</v>
@@ -1530,13 +1502,13 @@
         <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>10</v>
@@ -1555,13 +1527,13 @@
         <v>14</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>10</v>
@@ -1577,19 +1549,19 @@
         <v>yc15</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E16" s="1">
         <v>16</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1602,19 +1574,19 @@
         <v>yc16</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E17" s="1">
         <v>16</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1627,19 +1599,19 @@
         <v>yc17</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E18" s="1">
         <v>16</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1652,19 +1624,19 @@
         <v>yc18</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E19" s="1">
         <v>16</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1677,19 +1649,19 @@
         <v>yc19</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E20" s="1">
         <v>16</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1702,19 +1674,19 @@
         <v>yc20</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E21" s="1">
         <v>16</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1727,19 +1699,19 @@
         <v>yc21</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E22" s="1">
         <v>16</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1752,19 +1724,19 @@
         <v>yc22</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E23" s="1">
         <v>16</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1777,19 +1749,19 @@
         <v>yc23</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E24" s="1">
         <v>16</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1802,19 +1774,19 @@
         <v>yc24</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E25" s="1">
         <v>16</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1827,19 +1799,19 @@
         <v>yc25</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E26" s="1">
         <v>16</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1852,19 +1824,19 @@
         <v>yc26</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E27" s="1">
         <v>16</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1877,19 +1849,19 @@
         <v>yc27</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E28" s="1">
         <v>16</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1906,16 +1878,16 @@
         <v>byte30-byte33</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E29" s="1">
         <v>32</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1932,16 +1904,16 @@
         <v>byte34-byte37</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E30" s="1">
         <v>32</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1958,16 +1930,16 @@
         <v>byte38-byte41</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E31" s="1">
         <v>32</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1984,16 +1956,16 @@
         <v>byte42-byte45</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E32" s="1">
         <v>32</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2010,16 +1982,16 @@
         <v>byte46-byte49</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E33" s="1">
         <v>32</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2036,16 +2008,16 @@
         <v>byte50-byte53</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="E34" s="1">
         <v>32</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" ht="57" spans="1:7">
@@ -2058,10 +2030,10 @@
         <v>yc34</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E35" s="3">
         <v>4</v>
@@ -2083,19 +2055,19 @@
         <v>yc35</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E36" s="3">
         <v>12</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" ht="28.5" spans="1:7">
@@ -2108,10 +2080,10 @@
         <v>yc36</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E37" s="5">
         <v>1</v>
@@ -2133,19 +2105,19 @@
         <v>yc37</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E38" s="5">
         <v>16</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2158,19 +2130,19 @@
         <v>yc38</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E39" s="5">
         <v>15</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
